--- a/Shared/XLS/BanWord.xlsx
+++ b/Shared/XLS/BanWord.xlsx
@@ -3,11 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="#BanWord" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="#BadWord" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="#BadWord_KR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="#BadWord_US" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="#BadWord_JP" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -526,7 +528,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -538,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -549,8 +551,8 @@
     <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
     <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
     <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9" customWidth="1" style="1" min="9" max="10"/>
-    <col width="9" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="9" max="11"/>
+    <col width="9" customWidth="1" style="1" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -722,40 +724,9 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>運営</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>14</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -768,19 +739,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="6.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="9.375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
     <col width="23.75" customWidth="1" style="1" min="3" max="3"/>
     <col width="16.25" customWidth="1" style="1" min="4" max="4"/>
     <col width="16.5" customWidth="1" style="1" min="5" max="5"/>
     <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
     <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
     <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9" customWidth="1" style="1" min="9" max="10"/>
-    <col width="9" customWidth="1" style="1" min="11" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="9" max="11"/>
+    <col width="9" customWidth="1" style="1" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -791,7 +762,7 @@
       </c>
       <c r="B1" s="11" t="inlineStr">
         <is>
-          <t>BadWord</t>
+          <t>BadWord_KR</t>
         </is>
       </c>
       <c r="C1" s="9" t="n"/>
@@ -882,7 +853,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fuck</t>
+          <t>강간</t>
         </is>
       </c>
       <c r="D8" s="7" t="n"/>
@@ -894,29 +865,8876 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shit</t>
+          <t>개자식</t>
         </is>
       </c>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>개좆</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="2" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>개차반</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>거유</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>계집년</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>근친</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>니기미</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>뒤질래</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>딸딸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>때씹</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>또라이</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>뙤놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>로리타</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>몰카</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>미친새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>바바리맨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>변태</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>보지</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>불알</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>빠구리</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>사까시</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>섹스</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>스와핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>쌍놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>씨발놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>씨팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>씹물</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>씹빨</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>씹새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>씹알</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>씹창</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>씹팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>암캐</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>야동</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>야애니</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>엄창</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>염병</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>옘병</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>육갑</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>은꼴</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>자위</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>자지</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>잡년</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>종간나</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>좆만</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>죽일년</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>쥐좆</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>직촬</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>짱깨</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>쪽바리</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>창녀</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>포르노</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>화냥년</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>후레아들</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>후장</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>희쭈그리</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>D쥐고</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>D지고</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jonna</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jot같</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>mi쳤</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>tlqkf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>wlfkf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>같은새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>개나대</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>개념빠가</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>개련</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>개부랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>개새기</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>개섹</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>풀발</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>씹선</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>개쓰래기</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>개저씨</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>거지같</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>계새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>골빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>골1빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>괘새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>구1씹</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>구씹</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>87</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>그1켬</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>88</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>그지같</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>89</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>그켬</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>극1혐</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>91</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>극혐</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>92</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>글러먹</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>93</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>기레기</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>94</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>기자레기</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>김치녀</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>96</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>된장녀</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>97</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>앙기모띠</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>98</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>보적보</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>99</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>삼일한</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>100</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>보슬아치</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>101</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>보징어</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>102</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>엑윽</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>103</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>헤으응</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>104</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>부왘</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>105</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>보픈카</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>106</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>상폐녀</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>107</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>배빵</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>108</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>누보햄</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>109</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>찌질</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>110</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>자박꼼</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>111</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>쿰척</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>112</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>까내리</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>113</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>껒여</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>114</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>꺼지세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>115</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>꺼져요</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>116</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>로꺼져</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>117</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>꼬라지</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>118</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>꼴갑</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>119</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>꼴값</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>120</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>꼴깝</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>121</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>설거지론</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>122</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>퐁퐁남</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>123</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>퐁퐁녀</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>124</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>나빼썅</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>125</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>나쁜새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>126</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>넌씨눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>127</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>년놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>128</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>노무노무</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>129</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>노알라</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>130</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>노친네</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>131</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>느금</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>132</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>뇌텅</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>133</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>뇌1텅</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>134</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>눈깔파</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>135</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>눈새</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>136</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>늬믜</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>137</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>늬미</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>138</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>니년</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>139</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>니믜</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>140</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>니미럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>141</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>닝기리</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>142</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>다꺼져</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>143</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>닥쳐라</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>144</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>닥치세</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>145</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>덜떨어</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>146</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>도라이</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>147</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>도랏</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>148</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>도랐</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>149</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>돌앗구만</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>150</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>돌앗나</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>151</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>돌앗네</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>152</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>돌았구만</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>153</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>돌았나</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>154</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>돌았네</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>155</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>둄마</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>156</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>뒈져</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>157</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>뒤져라</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>158</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>뒤져버</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>159</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>뒤져야</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>160</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>뒤져야지</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>161</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>뒤져요</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>162</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>뒤지겠</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>163</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>뒤지고싶</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>164</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>뒤지길</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>165</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>뒤진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>166</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>디져라</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>167</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>디지고</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>168</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>딴년</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>169</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>또라인</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>170</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>똘아이</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>171</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>뚫린입</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>172</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>런년</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>173</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>레1친</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>174</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>레기같</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>175</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>레기네</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>176</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>레기다</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>177</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>레친</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>178</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>롬들</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>179</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>망돌</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>180</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>망해라</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>181</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>머갈</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>182</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>머리텅</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>183</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>명존</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>184</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>믜칀</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>185</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>믜친</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>186</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>미1친</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>187</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>미시친발</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>188</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>미쳣네</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>189</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>미쳤나</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>190</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>미쳤니</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>191</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>미췬</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>192</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>미칀</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>193</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>미친새</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>194</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>미친개</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>195</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>미친색</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>196</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>미틴</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>197</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>및힌</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>198</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>줘패</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>199</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>꼬추</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>200</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>색퀴</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>201</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>흉자</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>202</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>미친넘</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>203</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>미핀놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>204</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>샛기</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>205</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>G랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>206</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>미치누</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>207</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>d져</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>208</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>별창</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>209</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>병1신</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>210</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>보전깨</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>211</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>븅신</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>212</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>빠큐</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>213</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>빡새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>214</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>뻐규</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>215</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>뻐큐</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>216</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>뻑유</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>217</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>뻑큐</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>218</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>뻨큐</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>219</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>뼈큐</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>220</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>사새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>221</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>새1끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>222</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>새1키</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>223</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>새끼라</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>224</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>새끼야</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>225</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>새퀴</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>226</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>새킈</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>227</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>새키</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>228</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>색히</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>229</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>샊기</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>230</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>샊히</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>231</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>샹년</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>232</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>섀키</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>233</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>성괴</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>234</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>쉬발</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>235</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>쉬버</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>236</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>쉬이바</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>237</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>쉬펄</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>238</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>슈1발</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>239</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>슈레기</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>240</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>슈발</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>241</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>슈벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>242</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>슈우벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>243</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>스벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>244</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>싑창</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>245</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>시1발</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>246</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>시미발친</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>247</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>시미친발</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>248</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>시바라지</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>249</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>시바류</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>250</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>시바시바</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>251</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>시바알</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>252</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>시바앙</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>253</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>시방새</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>254</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>시벌탱</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>255</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>시볼탱</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>256</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>시부럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>257</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>시부렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>258</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>시부울</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>259</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>시뷰럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>260</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>시뷰렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>261</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>시빨</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>262</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>시새발끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>263</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>시이발</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>264</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>시친발미</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>265</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>시팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>266</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>시펄</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>267</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>십창</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>268</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>싸가지없</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>269</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>싸물어</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>270</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>쌍년</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>271</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>쌔끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>272</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>썌끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>273</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>쒸펄</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>274</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>쓰1레기</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>275</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>쓰래기같</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>276</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>쓰레기새</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>277</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>쓰렉</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>278</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>씝창</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>279</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>씨1발</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>280</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>씨바라</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>281</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>씨바알</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>282</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>씨방새</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>283</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>씨버럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>284</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>씨벌</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>285</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>씨벌탱</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>286</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>씨볼탱</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>287</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>씨부럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>288</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>씨부렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>289</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>씨뷰럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>290</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>씨뷰렬</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>291</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>씨빠빠</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>292</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>씨빨</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>293</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>씨뻘</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>294</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>씨새발끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>295</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>씨이발</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>296</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>씹귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>297</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>씹덕</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>298</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>씹못</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>299</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>씹뻐럴</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>300</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>씹쌔</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>301</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>씹치</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>302</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>씹할</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>303</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>아가리</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>304</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>아닥</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>305</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>아오시바</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>306</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>애미</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>307</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>앰창</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>308</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>에라이퉤</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>309</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>에라이퉷</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>310</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>엠뷩신</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>311</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>엠븽신</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>312</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>엠빙신</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>313</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>엠생</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>314</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>엠창</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>315</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>엿같</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>316</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>엿이나</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>317</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>와꾸</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>318</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>외1퀴</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>319</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>외퀴</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>320</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>은년</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>321</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>은새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>322</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>이새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>323</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>인간말종</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>324</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>입털</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>325</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>정신병자</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>326</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>정신나갓</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>327</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>정신나갔</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>328</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>젖같</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>329</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>젗같</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>330</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>젼나</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>331</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>젼낰</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>332</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>졌같은</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>333</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>졏같</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>334</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>조낸</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>335</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>조녜</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>336</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>조온나</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>337</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>족까</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>338</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>존나</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>339</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>존1나</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>340</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>존낙</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>341</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>존내</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>342</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>좁밥</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>343</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>조센징</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>344</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>짱개</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>345</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>짱꼴라</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>346</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>짱골라</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>347</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>종나</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>348</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>좆팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>349</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>후팔</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>350</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>좆까</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>351</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>좇같</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>352</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>좆되네</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>353</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>죠낸</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>354</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>죠온나</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>355</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>죤나</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>356</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>죤내</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>357</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>죵나</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>358</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>죽어버려</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>359</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>죽여버리고</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>360</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>죽여불고</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>361</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>죽여뿌고</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>362</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>줬같은</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>363</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>쥐랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>364</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>쥰나</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>365</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>쥰내</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>366</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>쥰니</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>367</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>쥰트</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>368</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>즤랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>369</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>지랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>370</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>지1랄</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>371</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>지롤</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>372</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>짱께</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>373</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>쪼녜</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>374</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>쪼다</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>375</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>착짱죽짱</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>376</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>섬숭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>377</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>쪽본</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>378</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>쪽1바리</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>379</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>쪽발</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>380</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>쫓같</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>381</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>쯰질</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>382</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>찌1질</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>383</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>찌질한</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>384</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>찝째끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>385</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>창년</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>386</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>창남</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>387</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>창놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>388</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>처먹</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>389</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>취좃</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>390</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>친년</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>391</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>친놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>392</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>친구년</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>393</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>친노마</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>394</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>텐덕</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>395</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>손놈</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>396</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>남미새</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>397</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>여미새</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>398</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>호로새끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>399</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>호로잡</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>400</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>화낭년</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>401</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>후1빨</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>402</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>후빨</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>403</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>닥쳐</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>404</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>등신</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>405</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>뇌텅텅</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>406</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>쌍판</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>407</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>자살</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H341"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="6.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12.625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="23.75" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.25" customWidth="1" style="1" min="4" max="4"/>
+    <col width="16.5" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9" customWidth="1" style="1" min="9" max="11"/>
+    <col width="9" customWidth="1" style="1" min="12" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" s="3">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>!Table</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>BadWord_US</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>!ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>!int</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>!string</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fuck</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>shit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2g1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2girls1cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>acrotomophilia</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>alabamahotpocket</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>alaskanpipeline</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>anilingus</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>apeshit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>arsehole</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>asshole</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>assmunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>autoerotic</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>babeland</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>babybatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>babyjuice</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ballgag</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ballgravy</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ballkicking</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>balllicking</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ballsack</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ballsucking</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bangbros</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bangbus</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bareback</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>barelylegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>barenaked</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bastardo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bastinado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bdsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>beaner</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>beaners</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>beavercleaver</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>beaverlips</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>beastiality</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bestiality</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bigbreasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bigknockers</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bigtits</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bimbos</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>birdlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bitches</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>blackcock</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>blondeaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>blondeonblondeaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>blowjob</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>blowyourload</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bluewaffle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>blumpkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bollocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bondage</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>boner</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>boob</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>boobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bootycall</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>brownshowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>brunetteaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bukkake</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>bulldyke</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bulletvibe</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bullshit</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>bunghole</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>busty</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>buttcheeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>butthole</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>cameltoe</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>camgirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>camslut</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>camwhore</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>carpetmuncher</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>chocolaterosebuds</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>circlejerk</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>clevelandsteamer</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>clit</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>clitoris</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>cloverclamps</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>clusterfuck</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>coprolagnia</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>coprophilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>cornhole</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>creampie</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cumming</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>cumshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>cumshots</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>87</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>cunnilingus</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>88</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>cunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>89</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>darkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>daterape</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>91</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>deepthroat</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>92</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dendrophilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>93</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dick</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>94</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dildo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dingleberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>96</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>dingleberries</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>97</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>dirtypillows</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>98</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>dirtysanchez</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>99</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>doggiestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>100</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>doggystyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>101</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>dogstyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>102</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>dolcett</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>103</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>dominatrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>104</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>dommes</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>105</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>donkeypunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>106</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>doubledong</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>107</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>doublepenetration</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>108</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>dpaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>109</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>dryhump</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>110</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>dvda</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>111</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>eatmyass</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>112</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ecchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>113</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ejaculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>114</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>erotic</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>115</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>erotism</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>116</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>eunuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>117</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>faggot</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>118</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>fecal</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>119</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>felch</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>120</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>fellatio</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>121</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>feltch</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>122</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>femalesquirting</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>123</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>femdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>124</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>figging</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>125</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>fingerbang</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>126</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>fingering</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>127</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>fisting</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>128</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>footfetish</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>129</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>footjob</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>130</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>frotting</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>131</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>fuckbuttons</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>132</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>fuckin</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>133</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>fucking</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>134</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>fucktards</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>135</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>fudgepacker</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>136</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>futanari</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>137</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>gangbang</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>138</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>gaysex</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>139</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>genitals</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>140</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>giantcock</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>141</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>girlon</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>142</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>girlontop</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>143</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>girlsgonewild</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>144</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>goatcx</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>145</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>goatse</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>146</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>goddamn</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>147</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>gokkun</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>148</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>goldenshower</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>149</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>goodpoop</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>150</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>googirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>151</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>goregasm</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>152</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>grope</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>153</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>groupsex</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>154</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>gspot</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>155</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>handjob</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>156</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>hentai</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>157</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>homoerotic</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>158</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>honkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>159</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>hooker</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>160</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>horny</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>161</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>hotcarl</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>162</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>hotchick</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>163</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>howtokill</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>164</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>howtomurder</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>165</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>hugefat</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>166</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>humping</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>167</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>incest</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>168</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>intercourse</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>169</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>jackoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>170</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>jailbait</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>171</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>jerkoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>172</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>jigaboo</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>173</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>jiggaboo</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>174</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>jiggerboo</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>175</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>jizz</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>176</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>juggs</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>177</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>kike</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>178</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>kinbaku</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>179</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>kinkster</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>180</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>kinky</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>181</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>knobbing</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>182</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>leatherrestraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>183</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>leatherstraightjacket</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>184</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>lemonparty</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>185</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>livesex</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>186</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>lolita</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>187</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>lovemaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>188</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>makemecome</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>189</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>malesquirting</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>190</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>masturbate</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>191</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>masturbating</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>192</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>masturbation</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>193</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>menageatrois</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>194</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>missionaryposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>195</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>motherfucker</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>196</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>moundofvenus</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>197</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>mrhands</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>198</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>muffdiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>199</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>muffdiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>200</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>nambla</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>201</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>nawashi</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>202</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>negro</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>203</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>neonazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>204</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>nigga</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>205</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>nigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>206</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>nignog</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>207</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>nimphomania</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>208</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>nipple</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>209</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>nipples</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>210</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>nsfw</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>211</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>nsfwimages</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>212</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>nude</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>213</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>nudity</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>214</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>nutten</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>215</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>nympho</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>216</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>nymphomania</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>217</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>octopussy</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>218</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>omorashi</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>219</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>onecuptwogirls</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>220</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>oneguyonejar</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>221</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>orgasm</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>222</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>orgy</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>223</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>paedophile</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>224</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>panties</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>225</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>panty</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>226</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>pedobear</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>227</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>pedophile</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>228</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>penis</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>229</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>phonesex</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>230</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>pieceofshit</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>231</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>pikey</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>232</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>pissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>233</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>pisspig</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>234</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>playboy</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>235</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>pleasurechest</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>236</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>polesmoker</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>237</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ponyplay</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>238</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>poontang</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>239</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>punany</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>240</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>poopchute</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>241</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>porn</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>242</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>porno</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>243</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>pornography</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>244</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>princealbertpiercing</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>245</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>pthc</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>246</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>pubes</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>247</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>pussy</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>248</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>queaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>249</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>queef</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>250</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>quim</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>251</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>raghead</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>252</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ragingboner</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>253</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>rectum</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>254</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>reversecowgirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>255</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>rimjob</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>256</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>rosypalm</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>257</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>rosypalmandher5sisters</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>258</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>rustytrombone</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>259</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sadism</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>260</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>schlong</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>261</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>scissoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>262</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sexcam</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>263</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>264</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sexy</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>265</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sexual</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>266</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sexually</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>267</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sexuality</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>268</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>shavedbeaver</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>269</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>shavedpussy</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>270</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>shemale</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>271</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>shibari</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>272</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>shitblimp</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>273</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>shitty</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>274</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>skeet</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>275</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>slanteye</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>276</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>slut</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>277</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>smut</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>278</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>sodomize</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>279</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sodomy</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>280</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>spastic</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>281</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>splooge</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>282</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>sploogemoose</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>283</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>spooge</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>284</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>spreadlegs</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>285</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>spunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>286</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>strapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>287</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>strappado</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>288</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>stripclub</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>289</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>styledoggy</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>290</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>suck</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>291</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>sucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>292</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>suicidegirls</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>293</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>sultrywomen</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>294</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>swastika</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>295</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>tastemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>296</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>teabagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>297</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>threesome</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>298</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>throating</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>299</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>thumbzilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>300</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>tiedup</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>301</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>tits</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>302</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>titties</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>303</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>titty</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>304</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>tongueina</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>305</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>topless</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>306</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>tosser</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>307</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>towelhead</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>308</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>tranny</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>309</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>tribadism</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>310</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>tubgirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>311</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>tushy</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>312</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>twat</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>313</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>twogirlsonecup</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>314</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>undressing</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>315</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>upskirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>316</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>urethraplay</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>317</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>urophilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>318</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>vagina</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>319</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>venusmound</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>320</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>viagra</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>321</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>vibrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>322</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>violetwand</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>323</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>vorarephilia</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>324</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>voyeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>325</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>voyeurweb</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>326</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>voyuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>327</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>vulva</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>328</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>wetback</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>329</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>wetdream</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>330</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>whitepower</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>331</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>whore</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>332</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>worldsex</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>333</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>wrappingmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>334</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>wrinkledstarfish</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>335</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>yaoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>336</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>yellowshowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>337</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>yiffy</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>338</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>zoophilia</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H133"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="6.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12.625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="23.75" customWidth="1" style="1" min="3" max="3"/>
+    <col width="16.25" customWidth="1" style="1" min="4" max="4"/>
+    <col width="16.5" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.75" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13.625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="18.5" customWidth="1" style="1" min="8" max="8"/>
+    <col width="9" customWidth="1" style="1" min="9" max="11"/>
+    <col width="9" customWidth="1" style="1" min="12" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" s="3">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>!Table</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>BadWord_JP</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>!ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>!int</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>!string</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ばか</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gスポット</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sm女王</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>アスホール</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>アナリングス</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>アナル</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>イラマチオ</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>エクスタシー</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>エッチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>エロティズム</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>エロティック</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>オーガズム</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>オカマ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>おしっこ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>おしり</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>オシリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>おしりのあな</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>おっぱい</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>オッパイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>オナニー</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>オマンコ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>おもらし</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>お尻</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>カーマスートラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>クリトリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>26</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>クンニリングス</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ゲイボーイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ゴールデンシャワー</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>コカイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ゴックン</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>31</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>サディズム</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>スウィンガー</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>33</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>スカートの中</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>スカトロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>35</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ストラップオン</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ストリップ劇場</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>スラット</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>38</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>セクシーな</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>セクシーな10代</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>セックス</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ソドミー</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>42</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ちんこ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>43</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ディック</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>44</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ディルド</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>45</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>デートレイプ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>テレフォンセックス</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ドッグスタイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>トップレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>49</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ニガー</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>パイパン</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>バイブレーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>パンティー</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>53</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ビッチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>54</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ファック</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>55</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>フェティッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>56</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>フェラチオ</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>57</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ふたなり</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>58</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>プリンスアルバートピアス</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>59</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>プレイボーイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>60</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ベアバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ペニス</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>62</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ペニスバンド</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ボールギャグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>64</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ホモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>65</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ポルノ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>66</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ポルノグラフィー</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ボンテージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>68</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>マスターベーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>69</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>まんこ</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>70</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>やおい</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>71</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>やりまん</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ランジェリー</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>レイプ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>74</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>レズビアン</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>75</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ロリータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>76</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>淫乱</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>77</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>陰毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>78</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>革抑制</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>79</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>騎上位</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>80</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>巨根</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>81</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>巨乳</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>82</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>強姦犯</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>83</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>玉なめ</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>84</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>玉舐め</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>緊縛</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>86</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>近親相姦</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>87</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>後背位</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>88</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>合意の性交</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>89</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>拷問</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>90</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>殺し方</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>91</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>殺人方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>92</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>児童性虐待</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>93</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>射精</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>94</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>手コキ</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>95</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>獣姦</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>96</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>新しいポルノ</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>97</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>人妻</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>98</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>性交</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>99</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>正常位</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>100</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>生殖器</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>101</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>精液</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>102</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>足フェチ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>103</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>足を広げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>104</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>大陰唇</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>105</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>脱衣</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>106</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>茶色のシャワー</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>107</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>中出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>108</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>潮吹き女</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>109</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>潮吹き男性</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>110</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>直腸</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>111</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>剃毛</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>112</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>貞操帯</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>113</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>奴隷</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>114</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>二穴</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>115</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>乳首</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>116</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>尿道プレイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>117</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>覗き</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>118</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>売春婦</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>119</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>糞尿愛好症</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>120</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>糞便</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>121</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>変態</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>122</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>勃起する</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>123</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>夢精</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>124</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>幼児性愛者</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>125</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>裸の女性</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>126</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>乱交</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>127</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>両性具有</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>128</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>輪姦</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>129</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>宦官</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>130</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>肛門</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>